--- a/public/Plantilla_MAYU_Materiales.xlsx
+++ b/public/Plantilla_MAYU_Materiales.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,11 +30,6 @@
     <font>
       <b val="1"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00666666"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -59,7 +54,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
+      <color rgb="000066CC"/>
       <sz val="10"/>
     </font>
     <font>
@@ -69,11 +64,11 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000066CC"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +83,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAFAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,36 +117,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +535,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Los ítems nuevos se agregan a la biblioteca. Códigos repetidos se actualizan. Solo se aceptan partidas y sublíneas de la lista.</t>
+          <t>Ítems nuevos se agregan a la biblioteca. Códigos repetidos se actualizan. Sublínea vacía = ítem fijo (siempre incluido).</t>
         </is>
       </c>
     </row>
@@ -3860,22 +3859,22 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B172 B173 B174 B175 B176 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B201 B202 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B222 B223 B224 B225 B226 B227 B228 B229 B230 B231 B232 B233 B234 B235 B236 B237 B238 B239 B240 B241 B242 B243 B244 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B258 B259 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B276 B277 B278 B279 B280 B281 B282 B283 B284 B285 B286 B287 B288 B289 B290 B291 B292 B293 B294 B295 B296 B297 B298 B299 B300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Partida no válida" error="Solo se permiten las 13 líneas de fabricación definidas." promptTitle="Partida" prompt="Seleccione la línea de fabricación del desplegable" type="list">
+    <dataValidation sqref="B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B63 B64 B65 B66 B67 B68 B69 B70 B71 B72 B73 B74 B75 B76 B77 B78 B79 B80 B81 B82 B83 B84 B85 B86 B87 B88 B89 B90 B91 B92 B93 B94 B95 B96 B97 B98 B99 B100 B101 B102 B103 B104 B105 B106 B107 B108 B109 B110 B111 B112 B113 B114 B115 B116 B117 B118 B119 B120 B121 B122 B123 B124 B125 B126 B127 B128 B129 B130 B131 B132 B133 B134 B135 B136 B137 B138 B139 B140 B141 B142 B143 B144 B145 B146 B147 B148 B149 B150 B151 B152 B153 B154 B155 B156 B157 B158 B159 B160 B161 B162 B163 B164 B165 B166 B167 B168 B169 B170 B171 B172 B173 B174 B175 B176 B177 B178 B179 B180 B181 B182 B183 B184 B185 B186 B187 B188 B189 B190 B191 B192 B193 B194 B195 B196 B197 B198 B199 B200 B201 B202 B203 B204 B205 B206 B207 B208 B209 B210 B211 B212 B213 B214 B215 B216 B217 B218 B219 B220 B221 B222 B223 B224 B225 B226 B227 B228 B229 B230 B231 B232 B233 B234 B235 B236 B237 B238 B239 B240 B241 B242 B243 B244 B245 B246 B247 B248 B249 B250 B251 B252 B253 B254 B255 B256 B257 B258 B259 B260 B261 B262 B263 B264 B265 B266 B267 B268 B269 B270 B271 B272 B273 B274 B275 B276 B277 B278 B279 B280 B281 B282 B283 B284 B285 B286 B287 B288 B289 B290 B291 B292 B293 B294 B295 B296 B297 B298 B299 B300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Partida no válida" error="Solo se permiten las 13 líneas de fabricación." promptTitle="Partida" prompt="Seleccione línea de fabricación" type="list">
       <formula1>"BASE,ESTRUCTURA,TECHO,ELECTRICO,SANITARIO AGUA POTABLE,SANITARIO ALCANTARILLADO,REVESTIMIENTO DE MURO,CIELO,SANITARIO ARTEFACTOS,TERMINACION DE MURO,PISO,PUERTAS,INSUMOS GENERALES"</formula1>
     </dataValidation>
-    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C107 C108 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C119 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C131 C132 C133 C134 C135 C136 C137 C138 C139 C140 C141 C142 C143 C144 C145 C146 C147 C148 C149 C150 C151 C152 C153 C154 C155 C156 C157 C158 C159 C160 C161 C162 C163 C164 C165 C166 C167 C168 C169 C170 C171 C172 C173 C174 C175 C176 C177 C178 C179 C180 C181 C182 C183 C184 C185 C186 C187 C188 C189 C190 C191 C192 C193 C194 C195 C196 C197 C198 C199 C200 C201 C202 C203 C204 C205 C206 C207 C208 C209 C210 C211 C212 C213 C214 C215 C216 C217 C218 C219 C220 C221 C222 C223 C224 C225 C226 C227 C228 C229 C230 C231 C232 C233 C234 C235 C236 C237 C238 C239 C240 C241 C242 C243 C244 C245 C246 C247 C248 C249 C250 C251 C252 C253 C254 C255 C256 C257 C258 C259 C260 C261 C262 C263 C264 C265 C266 C267 C268 C269 C270 C271 C272 C273 C274 C275 C276 C277 C278 C279 C280 C281 C282 C283 C284 C285 C286 C287 C288 C289 C290 C291 C292 C293 C294 C295 C296 C297 C298 C299 C300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sublínea no válida" error="Solo se permiten las sublíneas definidas. Deje vacío para ítems fijos." promptTitle="Sublínea" prompt="Solo para: Term. Muro, Piso, Artefactos, Rev. Muro, Puertas. Vacío = ítem fijo." type="list">
-      <formula1>"(sin sublínea),ceramica,pintura,pintura_latex,pintura_esmalte,vinilico,porcelanato,tina,wc_tanque,wc_taza,wc_asiento,lavamanos,pedestal,grif_lav,grif_tina,extractor,revRH125,revRF125,revST125,revST10,revFibro,puerta,cerradura"</formula1>
+    <dataValidation sqref="C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62 C63 C64 C65 C66 C67 C68 C69 C70 C71 C72 C73 C74 C75 C76 C77 C78 C79 C80 C81 C82 C83 C84 C85 C86 C87 C88 C89 C90 C91 C92 C93 C94 C95 C96 C97 C98 C99 C100 C101 C102 C103 C104 C105 C106 C107 C108 C109 C110 C111 C112 C113 C114 C115 C116 C117 C118 C119 C120 C121 C122 C123 C124 C125 C126 C127 C128 C129 C130 C131 C132 C133 C134 C135 C136 C137 C138 C139 C140 C141 C142 C143 C144 C145 C146 C147 C148 C149 C150 C151 C152 C153 C154 C155 C156 C157 C158 C159 C160 C161 C162 C163 C164 C165 C166 C167 C168 C169 C170 C171 C172 C173 C174 C175 C176 C177 C178 C179 C180 C181 C182 C183 C184 C185 C186 C187 C188 C189 C190 C191 C192 C193 C194 C195 C196 C197 C198 C199 C200 C201 C202 C203 C204 C205 C206 C207 C208 C209 C210 C211 C212 C213 C214 C215 C216 C217 C218 C219 C220 C221 C222 C223 C224 C225 C226 C227 C228 C229 C230 C231 C232 C233 C234 C235 C236 C237 C238 C239 C240 C241 C242 C243 C244 C245 C246 C247 C248 C249 C250 C251 C252 C253 C254 C255 C256 C257 C258 C259 C260 C261 C262 C263 C264 C265 C266 C267 C268 C269 C270 C271 C272 C273 C274 C275 C276 C277 C278 C279 C280 C281 C282 C283 C284 C285 C286 C287 C288 C289 C290 C291 C292 C293 C294 C295 C296 C297 C298 C299 C300" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Sublínea no válida" error="Use valores exactos: tina, ceramica, revRH125, puerta, etc. Vacío = ítem fijo." promptTitle="Sublínea" prompt="Vacío = fijo. Valores: tina, wc_tanque, lavamanos, ceramica, pintura, revRH125, puerta, etc." type="list">
+      <formula1>"tina,wc_tanque,wc_taza,wc_asiento,lavamanos,pedestal,grif_lav,grif_tina,extractor,ceramica,pintura,pintura_latex,pintura_esmalte,vinilico,porcelanato,revRH125,revRF125,revST125,revST10,revFibro,puerta,cerradura"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201 F202 F203 F204 F205 F206 F207 F208 F209 F210 F211 F212 F213 F214 F215 F216 F217 F218 F219 F220 F221 F222 F223 F224 F225 F226 F227 F228 F229 F230 F231 F232 F233 F234 F235 F236 F237 F238 F239 F240 F241 F242 F243 F244 F245 F246 F247 F248 F249 F250 F251 F252 F253 F254 F255 F256 F257 F258 F259 F260 F261 F262 F263 F264 F265 F266 F267 F268 F269 F270 F271 F272 F273 F274 F275 F276 F277 F278 F279 F280 F281 F282 F283 F284 F285 F286 F287 F288 F289 F290 F291 F292 F293 F294 F295 F296 F297 F298 F299 F300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Unidad no válida" error="Seleccione una unidad de la lista." type="list">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F59 F60 F61 F62 F63 F64 F65 F66 F67 F68 F69 F70 F71 F72 F73 F74 F75 F76 F77 F78 F79 F80 F81 F82 F83 F84 F85 F86 F87 F88 F89 F90 F91 F92 F93 F94 F95 F96 F97 F98 F99 F100 F101 F102 F103 F104 F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F119 F120 F121 F122 F123 F124 F125 F126 F127 F128 F129 F130 F131 F132 F133 F134 F135 F136 F137 F138 F139 F140 F141 F142 F143 F144 F145 F146 F147 F148 F149 F150 F151 F152 F153 F154 F155 F156 F157 F158 F159 F160 F161 F162 F163 F164 F165 F166 F167 F168 F169 F170 F171 F172 F173 F174 F175 F176 F177 F178 F179 F180 F181 F182 F183 F184 F185 F186 F187 F188 F189 F190 F191 F192 F193 F194 F195 F196 F197 F198 F199 F200 F201 F202 F203 F204 F205 F206 F207 F208 F209 F210 F211 F212 F213 F214 F215 F216 F217 F218 F219 F220 F221 F222 F223 F224 F225 F226 F227 F228 F229 F230 F231 F232 F233 F234 F235 F236 F237 F238 F239 F240 F241 F242 F243 F244 F245 F246 F247 F248 F249 F250 F251 F252 F253 F254 F255 F256 F257 F258 F259 F260 F261 F262 F263 F264 F265 F266 F267 F268 F269 F270 F271 F272 F273 F274 F275 F276 F277 F278 F279 F280 F281 F282 F283 F284 F285 F286 F287 F288 F289 F290 F291 F292 F293 F294 F295 F296 F297 F298 F299 F300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Unidad no válida" error="Seleccione de la lista." type="list">
       <formula1>"UNIDAD,MT LINEAL,MT2,KG,CAJA,LITRO,GALON,ROLLO,SET,SACO,PAR"</formula1>
     </dataValidation>
-    <dataValidation sqref="G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 G205 G206 G207 G208 G209 G210 G211 G212 G213 G214 G215 G216 G217 G218 G219 G220 G221 G222 G223 G224 G225 G226 G227 G228 G229 G230 G231 G232 G233 G234 G235 G236 G237 G238 G239 G240 G241 G242 G243 G244 G245 G246 G247 G248 G249 G250 G251 G252 G253 G254 G255 G256 G257 G258 G259 G260 G261 G262 G263 G264 G265 G266 G267 G268 G269 G270 G271 G272 G273 G274 G275 G276 G277 G278 G279 G280 G281 G282 G283 G284 G285 G286 G287 G288 G289 G290 G291 G292 G293 G294 G295 G296 G297 G298 G299 G300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Presentación no válida" error="Seleccione una presentación de la lista." type="list">
+    <dataValidation sqref="G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 G105 G106 G107 G108 G109 G110 G111 G112 G113 G114 G115 G116 G117 G118 G119 G120 G121 G122 G123 G124 G125 G126 G127 G128 G129 G130 G131 G132 G133 G134 G135 G136 G137 G138 G139 G140 G141 G142 G143 G144 G145 G146 G147 G148 G149 G150 G151 G152 G153 G154 G155 G156 G157 G158 G159 G160 G161 G162 G163 G164 G165 G166 G167 G168 G169 G170 G171 G172 G173 G174 G175 G176 G177 G178 G179 G180 G181 G182 G183 G184 G185 G186 G187 G188 G189 G190 G191 G192 G193 G194 G195 G196 G197 G198 G199 G200 G201 G202 G203 G204 G205 G206 G207 G208 G209 G210 G211 G212 G213 G214 G215 G216 G217 G218 G219 G220 G221 G222 G223 G224 G225 G226 G227 G228 G229 G230 G231 G232 G233 G234 G235 G236 G237 G238 G239 G240 G241 G242 G243 G244 G245 G246 G247 G248 G249 G250 G251 G252 G253 G254 G255 G256 G257 G258 G259 G260 G261 G262 G263 G264 G265 G266 G267 G268 G269 G270 G271 G272 G273 G274 G275 G276 G277 G278 G279 G280 G281 G282 G283 G284 G285 G286 G287 G288 G289 G290 G291 G292 G293 G294 G295 G296 G297 G298 G299 G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Unidad,Caja,Saco,Rollo,Tineta,Galón,kg,MT2,metro lineal,Bolsa,Tira,Set,Pieza,fijo"</formula1>
     </dataValidation>
-    <dataValidation sqref="H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H99 H100 H101 H102 H103 H104 H105 H106 H107 H108 H109 H110 H111 H112 H113 H114 H115 H116 H117 H118 H119 H120 H121 H122 H123 H124 H125 H126 H127 H128 H129 H130 H131 H132 H133 H134 H135 H136 H137 H138 H139 H140 H141 H142 H143 H144 H145 H146 H147 H148 H149 H150 H151 H152 H153 H154 H155 H156 H157 H158 H159 H160 H161 H162 H163 H164 H165 H166 H167 H168 H169 H170 H171 H172 H173 H174 H175 H176 H177 H178 H179 H180 H181 H182 H183 H184 H185 H186 H187 H188 H189 H190 H191 H192 H193 H194 H195 H196 H197 H198 H199 H200 H201 H202 H203 H204 H205 H206 H207 H208 H209 H210 H211 H212 H213 H214 H215 H216 H217 H218 H219 H220 H221 H222 H223 H224 H225 H226 H227 H228 H229 H230 H231 H232 H233 H234 H235 H236 H237 H238 H239 H240 H241 H242 H243 H244 H245 H246 H247 H248 H249 H250 H251 H252 H253 H254 H255 H256 H257 H258 H259 H260 H261 H262 H263 H264 H265 H266 H267 H268 H269 H270 H271 H272 H273 H274 H275 H276 H277 H278 H279 H280 H281 H282 H283 H284 H285 H286 H287 H288 H289 H290 H291 H292 H293 H294 H295 H296 H297 H298 H299 H300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Costo inválido" error="Ingrese un número positivo." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H99 H100 H101 H102 H103 H104 H105 H106 H107 H108 H109 H110 H111 H112 H113 H114 H115 H116 H117 H118 H119 H120 H121 H122 H123 H124 H125 H126 H127 H128 H129 H130 H131 H132 H133 H134 H135 H136 H137 H138 H139 H140 H141 H142 H143 H144 H145 H146 H147 H148 H149 H150 H151 H152 H153 H154 H155 H156 H157 H158 H159 H160 H161 H162 H163 H164 H165 H166 H167 H168 H169 H170 H171 H172 H173 H174 H175 H176 H177 H178 H179 H180 H181 H182 H183 H184 H185 H186 H187 H188 H189 H190 H191 H192 H193 H194 H195 H196 H197 H198 H199 H200 H201 H202 H203 H204 H205 H206 H207 H208 H209 H210 H211 H212 H213 H214 H215 H216 H217 H218 H219 H220 H221 H222 H223 H224 H225 H226 H227 H228 H229 H230 H231 H232 H233 H234 H235 H236 H237 H238 H239 H240 H241 H242 H243 H244 H245 H246 H247 H248 H249 H250 H251 H252 H253 H254 H255 H256 H257 H258 H259 H260 H261 H262 H263 H264 H265 H266 H267 H268 H269 H270 H271 H272 H273 H274 H275 H276 H277 H278 H279 H280 H281 H282 H283 H284 H285 H286 H287 H288 H289 H290 H291 H292 H293 H294 H295 H296 H297 H298 H299 H300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Costo inválido" error="Número positivo." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146 I147 I148 I149 I150 I151 I152 I153 I154 I155 I156 I157 I158 I159 I160 I161 I162 I163 I164 I165 I166 I167 I168 I169 I170 I171 I172 I173 I174 I175 I176 I177 I178 I179 I180 I181 I182 I183 I184 I185 I186 I187 I188 I189 I190 I191 I192 I193 I194 I195 I196 I197 I198 I199 I200 I201 I202 I203 I204 I205 I206 I207 I208 I209 I210 I211 I212 I213 I214 I215 I216 I217 I218 I219 I220 I221 I222 I223 I224 I225 I226 I227 I228 I229 I230 I231 I232 I233 I234 I235 I236 I237 I238 I239 I240 I241 I242 I243 I244 I245 I246 I247 I248 I249 I250 I251 I252 I253 I254 I255 I256 I257 I258 I259 I260 I261 I262 I263 I264 I265 I266 I267 I268 I269 I270 I271 I272 I273 I274 I275 I276 I277 I278 I279 I280 I281 I282 I283 I284 I285 I286 I287 I288 I289 I290 I291 I292 I293 I294 I295 I296 I297 I298 I299 I300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Cantidad inválida" error="Ingrese un número positivo." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 I105 I106 I107 I108 I109 I110 I111 I112 I113 I114 I115 I116 I117 I118 I119 I120 I121 I122 I123 I124 I125 I126 I127 I128 I129 I130 I131 I132 I133 I134 I135 I136 I137 I138 I139 I140 I141 I142 I143 I144 I145 I146 I147 I148 I149 I150 I151 I152 I153 I154 I155 I156 I157 I158 I159 I160 I161 I162 I163 I164 I165 I166 I167 I168 I169 I170 I171 I172 I173 I174 I175 I176 I177 I178 I179 I180 I181 I182 I183 I184 I185 I186 I187 I188 I189 I190 I191 I192 I193 I194 I195 I196 I197 I198 I199 I200 I201 I202 I203 I204 I205 I206 I207 I208 I209 I210 I211 I212 I213 I214 I215 I216 I217 I218 I219 I220 I221 I222 I223 I224 I225 I226 I227 I228 I229 I230 I231 I232 I233 I234 I235 I236 I237 I238 I239 I240 I241 I242 I243 I244 I245 I246 I247 I248 I249 I250 I251 I252 I253 I254 I255 I256 I257 I258 I259 I260 I261 I262 I263 I264 I265 I266 I267 I268 I269 I270 I271 I272 I273 I274 I275 I276 I277 I278 I279 I280 I281 I282 I283 I284 I285 I286 I287 I288 I289 I290 I291 I292 I293 I294 I295 I296 I297 I298 I299 I300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Cantidad inválida" error="Número positivo." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -3889,7 +3888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3919,31 +3918,6 @@
           <t>PRESENTACIONES</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
-        <is>
-          <t>Sub: TERM. MURO</t>
-        </is>
-      </c>
-      <c r="G1" s="11" t="inlineStr">
-        <is>
-          <t>Sub: PISO</t>
-        </is>
-      </c>
-      <c r="H1" s="11" t="inlineStr">
-        <is>
-          <t>Sub: ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="I1" s="11" t="inlineStr">
-        <is>
-          <t>Sub: REV. MURO</t>
-        </is>
-      </c>
-      <c r="J1" s="11" t="inlineStr">
-        <is>
-          <t>Sub: PUERTAS</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3953,7 +3927,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(sin sublínea)</t>
+          <t>tina</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3964,31 +3938,6 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>Unidad</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ceramica</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ceramica</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>tina</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>revRH125</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>puerta</t>
         </is>
       </c>
     </row>
@@ -4000,7 +3949,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ceramica</t>
+          <t>wc_tanque</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4011,31 +3960,6 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>Caja</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>pintura</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>vinilico</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>wc_tanque</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>revRF125</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>cerradura</t>
         </is>
       </c>
     </row>
@@ -4047,7 +3971,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pintura</t>
+          <t>wc_taza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4058,26 +3982,6 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>Saco</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>pintura_latex</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>porcelanato</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>wc_taza</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>revST125</t>
         </is>
       </c>
     </row>
@@ -4089,7 +3993,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pintura_latex</t>
+          <t>wc_asiento</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4100,21 +4004,6 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Rollo</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>pintura_esmalte</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>wc_asiento</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>revST10</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4015,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pintura_esmalte</t>
+          <t>lavamanos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4137,16 +4026,6 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>Tineta</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>lavamanos</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>revFibro</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4037,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vinilico</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4169,11 +4048,6 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>Galón</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>pedestal</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4059,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>porcelanato</t>
+          <t>grif_lav</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4196,11 +4070,6 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>kg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>grif_lav</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4081,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tina</t>
+          <t>grif_tina</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4223,11 +4092,6 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>MT2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>grif_tina</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4103,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>wc_tanque</t>
+          <t>extractor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4250,11 +4114,6 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>metro lineal</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>extractor</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4125,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wc_taza</t>
+          <t>ceramica</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4288,7 +4147,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wc_asiento</t>
+          <t>pintura</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4310,7 +4169,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lavamanos</t>
+          <t>pintura_latex</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4327,7 +4186,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pedestal</t>
+          <t>pintura_esmalte</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4339,7 +4198,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>grif_lav</t>
+          <t>vinilico</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4351,61 +4210,54 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>grif_tina</t>
+          <t>porcelanato</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>extractor</t>
+          <t>revRH125</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>revRH125</t>
+          <t>revRF125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>revRF125</t>
+          <t>revST125</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>revST125</t>
+          <t>revST10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>revST10</t>
+          <t>revFibro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>revFibro</t>
+          <t>puerta</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
-        <is>
-          <t>puerta</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
         <is>
           <t>cerradura</t>
         </is>
@@ -4423,547 +4275,496 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>PARTIDA</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
-        <is>
-          <t>SUBLÍNEA</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>DESCRIPCIÓN / CUÁNDO USAR</t>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>VALOR SUBLÍNEA (exacto)</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
-      <c r="B2" s="14" t="inlineStr"/>
-      <c r="C2" s="13" t="inlineStr"/>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>tina</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Tina o receptáculo de ducha</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>wc_tanque</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Estanque WC</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>wc_taza</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Taza WC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>wc_asiento</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Asiento WC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>lavamanos</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Lavamanos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>pedestal</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Pedestal o mueble bajo lavamanos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>grif_lav</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Grifería lavamanos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>grif_tina</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Grifería tina/ducha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>SANITARIO ARTEFACTOS</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>extractor</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Extractor de baño</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr"/>
+      <c r="B11" s="14" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>TERMINACION DE MURO</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>ceramica</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Adhesivo cerámico, fragüe, espaciadores, esquineros</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>TERMINACION DE MURO</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>pintura</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Pasta muro (base para pintar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>TERMINACION DE MURO</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>pintura_latex</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Pintura látex (acabado final)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>TERMINACION DE MURO</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>pintura_esmalte</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Pintura esmalte al agua (acabado final)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="B16" s="14" t="inlineStr"/>
+      <c r="C16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>ceramica</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Cerámica de piso</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>vinilico</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Piso vinílico</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>PISO</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>porcelanato</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Porcelanato</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="14" t="inlineStr"/>
+      <c r="C20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>REVESTIMIENTO DE MURO</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>revRH125</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Plancha YC zona húmeda (RH 12.5mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>REVESTIMIENTO DE MURO</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>revRF125</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Plancha YC protección fuego (RF 12.5mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>REVESTIMIENTO DE MURO</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>revST125</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Plancha YC zona seca (ST 12.5mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>REVESTIMIENTO DE MURO</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>revST10</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Plancha YC shaft (ST 10mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>REVESTIMIENTO DE MURO</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>revFibro</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Plancha fibrocemento faldón tina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr"/>
+      <c r="B26" s="14" t="inlineStr"/>
+      <c r="C26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>PUERTAS</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>puerta</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Puerta (seleccionable por el comercial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>PUERTAS</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>cerradura</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Cerradura (seleccionable por el comercial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr"/>
+      <c r="B29" s="14" t="inlineStr"/>
+      <c r="C29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>NOTA IMPORTANTE</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr"/>
+      <c r="C30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>Las demás partidas</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>(dejar vacío)</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Insumo fijo — siempre incluido (Cave Polflex, guardapolvo, molduras)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>TERMINACION DE MURO</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>ceramica</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Adhesivo cerámico, fragüe, espaciadores, esquineros</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>TERMINACION DE MURO</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>pintura</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Pasta muro (base para pintar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>TERMINACION DE MURO</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>pintura_latex</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Pintura látex (acabado final)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>TERMINACION DE MURO</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>pintura_esmalte</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Pintura esmalte al agua (acabado final)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr"/>
-      <c r="B8" s="14" t="inlineStr"/>
-      <c r="C8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>(dejar vacío)</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Insumo fijo de piso</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>ceramica</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Cerámica de piso (ej: 30x30, 45x45)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>vinilico</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Piso vinílico</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>PISO</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>porcelanato</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Porcelanato</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr"/>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>(dejar vacío)</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Insumo fijo — siempre incluido (sellos, celosías, soportes)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>tina</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Tina o receptáculo de ducha</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>wc_tanque</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Estanque WC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>wc_taza</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Taza WC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>wc_asiento</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Asiento WC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>lavamanos</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Lavamanos</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>pedestal</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Pedestal o mueble bajo lavamanos</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>grif_lav</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Grifería lavamanos</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>grif_tina</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Grifería tina/ducha</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>SANITARIO ARTEFACTOS</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>extractor</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Extractor de baño</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr"/>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>REVESTIMIENTO DE MURO</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>(dejar vacío)</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Insumo fijo — siempre incluido (masilla, sellante, aislación)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>REVESTIMIENTO DE MURO</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>revRH125</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Plancha yeso cartón RH 12.5mm (zona húmeda)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>REVESTIMIENTO DE MURO</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>revRF125</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>Plancha yeso cartón RF 12.5mm (protección fuego)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>REVESTIMIENTO DE MURO</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>revST125</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Plancha yeso cartón ST 12.5mm (zona seca)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>REVESTIMIENTO DE MURO</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>revST10</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Plancha yeso cartón ST 10mm (shaft)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>REVESTIMIENTO DE MURO</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>revFibro</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Plancha fibrocemento 6mm (faldón tina)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr"/>
-      <c r="B31" s="14" t="inlineStr"/>
-      <c r="C31" s="13" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>BASE, ESTRUCTURA, TECHO, ELÉCTRICO, SANITARIO AP/ALC, CIELO, INSUMOS → no usan sublínea</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>PUERTAS</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>(dejar vacío)</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Insumo fijo — siempre incluido (bisagras, topes)</t>
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Ítem con sublínea</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr"/>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Aparece como OPCIÓN seleccionable en el configurador (no suma costo automático)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>PUERTAS</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>puerta</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Puerta (seleccionable por el comercial)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>PUERTAS</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>cerradura</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Cerradura (seleccionable por el comercial)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr"/>
-      <c r="B35" s="14" t="inlineStr"/>
-      <c r="C35" s="13" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NOTA:</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr"/>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>Las partidas BASE, ESTRUCTURA, TECHO, ELÉCTRICO, SANITARIO AP/ALC, CIELO e INSUMOS no usan sublínea.</t>
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Ítem sin sublínea</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr"/>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>Se incluye SIEMPRE como insumo fijo en el costo del POD</t>
         </is>
       </c>
     </row>
